--- a/Demoblaze.xlsx
+++ b/Demoblaze.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="6"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="home" sheetId="4" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="26">
   <si>
     <t>c</t>
   </si>
@@ -40,9 +40,6 @@
     <t>Click</t>
   </si>
   <si>
-    <t>Login</t>
-  </si>
-  <si>
     <t>Username</t>
   </si>
   <si>
@@ -65,6 +62,42 @@
   </si>
   <si>
     <t>khushi987</t>
+  </si>
+  <si>
+    <t>Click Login</t>
+  </si>
+  <si>
+    <t>Click Logout</t>
+  </si>
+  <si>
+    <t>Enter Email</t>
+  </si>
+  <si>
+    <t>Enter Name</t>
+  </si>
+  <si>
+    <t>Enter Message</t>
+  </si>
+  <si>
+    <t>a@gmail.com</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>Hello From Tops</t>
+  </si>
+  <si>
+    <t>Click Submit</t>
+  </si>
+  <si>
+    <t>About</t>
+  </si>
+  <si>
+    <t>Click Play</t>
+  </si>
+  <si>
+    <t>Close</t>
   </si>
 </sst>
 </file>
@@ -439,19 +472,147 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B1" r:id="rId1"/>
+    <hyperlink ref="B5" r:id="rId2"/>
+    <hyperlink ref="B9" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -472,7 +633,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.140625" customWidth="1"/>
@@ -481,23 +642,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="3">
         <v>1234</v>
@@ -505,7 +666,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -513,49 +674,73 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1234</v>
+        <v>6</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1234</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
         <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1234</v>
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -575,23 +760,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="3">
         <v>1234</v>
@@ -599,7 +784,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -607,15 +792,15 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3">
         <v>1234</v>
@@ -623,7 +808,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -631,15 +816,15 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3">
         <v>1234</v>
@@ -647,7 +832,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -687,7 +872,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
